--- a/auswertung-beispiel2/data/01_Antraege.xlsx
+++ b/auswertung-beispiel2/data/01_Antraege.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -11574,7 +11574,7 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -11889,7 +11889,7 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11979,7 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -12519,7 +12519,7 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -12654,7 +12654,7 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -12699,7 +12699,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -13149,7 +13149,7 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -13239,7 +13239,7 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -13374,7 +13374,7 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -13419,7 +13419,7 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -13644,7 +13644,7 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -13689,7 +13689,7 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13734,7 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -13914,7 +13914,7 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -14139,7 +14139,7 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -14229,7 +14229,7 @@
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -14274,7 +14274,7 @@
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -14319,7 +14319,7 @@
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -14769,7 +14769,7 @@
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -14814,7 +14814,7 @@
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -15084,7 +15084,7 @@
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -15129,7 +15129,7 @@
       </c>
       <c r="I326" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="I327" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -15399,7 +15399,7 @@
       </c>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="I335" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="I336" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="I337" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -15669,7 +15669,7 @@
       </c>
       <c r="I338" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="I340" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="I341" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="I342" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -15894,7 +15894,7 @@
       </c>
       <c r="I343" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="I344" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="I345" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="I346" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="I347" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="I348" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -16164,7 +16164,7 @@
       </c>
       <c r="I349" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="I350" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="I351" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -16299,7 +16299,7 @@
       </c>
       <c r="I352" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="I353" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -16389,7 +16389,7 @@
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="I355" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="I357" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -16659,7 +16659,7 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -16839,7 +16839,7 @@
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -17064,7 +17064,7 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -17244,7 +17244,7 @@
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -17379,7 +17379,7 @@
       </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -17559,7 +17559,7 @@
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="I381" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -17694,7 +17694,7 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -17739,7 +17739,7 @@
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -17784,7 +17784,7 @@
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -17829,7 +17829,7 @@
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -17874,7 +17874,7 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -18009,7 +18009,7 @@
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -18054,7 +18054,7 @@
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -18099,7 +18099,7 @@
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -18144,7 +18144,7 @@
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -18279,7 +18279,7 @@
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="I399" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -18459,7 +18459,7 @@
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -18504,7 +18504,7 @@
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -18549,7 +18549,7 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -18594,7 +18594,7 @@
       </c>
       <c r="I403" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -18684,7 +18684,7 @@
       </c>
       <c r="I405" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="I406" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -18864,7 +18864,7 @@
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -18909,7 +18909,7 @@
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -18954,7 +18954,7 @@
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -18999,7 +18999,7 @@
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="I413" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -19089,7 +19089,7 @@
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -19179,7 +19179,7 @@
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -19224,7 +19224,7 @@
       </c>
       <c r="I417" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -19269,7 +19269,7 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -19314,7 +19314,7 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="I426" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -19674,7 +19674,7 @@
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -19719,7 +19719,7 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -19764,7 +19764,7 @@
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -20124,7 +20124,7 @@
       </c>
       <c r="I437" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -20304,7 +20304,7 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -20349,7 +20349,7 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -20439,7 +20439,7 @@
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -20484,7 +20484,7 @@
       </c>
       <c r="I445" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -20574,7 +20574,7 @@
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -20664,7 +20664,7 @@
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -20709,7 +20709,7 @@
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="I451" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -20799,7 +20799,7 @@
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -21024,7 +21024,7 @@
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -21069,7 +21069,7 @@
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -21159,7 +21159,7 @@
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -21204,7 +21204,7 @@
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -21249,7 +21249,7 @@
       </c>
       <c r="I462" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="I463" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -21339,7 +21339,7 @@
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="I465" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="I466" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -21474,7 +21474,7 @@
       </c>
       <c r="I467" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -21519,7 +21519,7 @@
       </c>
       <c r="I468" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -21564,7 +21564,7 @@
       </c>
       <c r="I469" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="I471" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="I472" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -21744,7 +21744,7 @@
       </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="I474" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -21834,7 +21834,7 @@
       </c>
       <c r="I475" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -21879,7 +21879,7 @@
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -21969,7 +21969,7 @@
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -22059,7 +22059,7 @@
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -22104,7 +22104,7 @@
       </c>
       <c r="I481" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -22149,7 +22149,7 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="I483" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -22374,7 +22374,7 @@
       </c>
       <c r="I487" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -22419,7 +22419,7 @@
       </c>
       <c r="I488" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -22464,7 +22464,7 @@
       </c>
       <c r="I489" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -22509,7 +22509,7 @@
       </c>
       <c r="I490" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -22554,7 +22554,7 @@
       </c>
       <c r="I491" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -22599,7 +22599,7 @@
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -22644,7 +22644,7 @@
       </c>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -22689,7 +22689,7 @@
       </c>
       <c r="I494" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -22734,7 +22734,7 @@
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -22779,7 +22779,7 @@
       </c>
       <c r="I496" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -22824,7 +22824,7 @@
       </c>
       <c r="I497" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="I498" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -22914,7 +22914,7 @@
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="I500" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -23004,7 +23004,7 @@
       </c>
       <c r="I501" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -23049,7 +23049,7 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -23094,7 +23094,7 @@
       </c>
       <c r="I503" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -23139,7 +23139,7 @@
       </c>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -23184,7 +23184,7 @@
       </c>
       <c r="I505" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -23229,7 +23229,7 @@
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="I507" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -23319,7 +23319,7 @@
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -23364,7 +23364,7 @@
       </c>
       <c r="I509" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -23409,7 +23409,7 @@
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="I511" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -23499,7 +23499,7 @@
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -23544,7 +23544,7 @@
       </c>
       <c r="I513" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -23589,7 +23589,7 @@
       </c>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -23634,7 +23634,7 @@
       </c>
       <c r="I515" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -23679,7 +23679,7 @@
       </c>
       <c r="I516" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="I517" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -23769,7 +23769,7 @@
       </c>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -23814,7 +23814,7 @@
       </c>
       <c r="I519" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -23859,7 +23859,7 @@
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -23904,7 +23904,7 @@
       </c>
       <c r="I521" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -23949,7 +23949,7 @@
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -23994,7 +23994,7 @@
       </c>
       <c r="I523" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="I524" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -24084,7 +24084,7 @@
       </c>
       <c r="I525" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="I526" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Bremshebel am Kinderwagen greift nicht mehr zuverlässig.</t>
         </is>
       </c>
     </row>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="I527" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -24219,7 +24219,7 @@
       </c>
       <c r="I528" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -24264,7 +24264,7 @@
       </c>
       <c r="I529" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="I530" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -24354,7 +24354,7 @@
       </c>
       <c r="I531" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -24399,7 +24399,7 @@
       </c>
       <c r="I532" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -24444,7 +24444,7 @@
       </c>
       <c r="I533" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -24489,7 +24489,7 @@
       </c>
       <c r="I534" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="I535" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -24579,7 +24579,7 @@
       </c>
       <c r="I536" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="I537" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -24669,7 +24669,7 @@
       </c>
       <c r="I538" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -24714,7 +24714,7 @@
       </c>
       <c r="I539" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -24759,7 +24759,7 @@
       </c>
       <c r="I540" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -24804,7 +24804,7 @@
       </c>
       <c r="I541" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -24849,7 +24849,7 @@
       </c>
       <c r="I542" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -24894,7 +24894,7 @@
       </c>
       <c r="I543" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -24939,7 +24939,7 @@
       </c>
       <c r="I544" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="I545" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -25029,7 +25029,7 @@
       </c>
       <c r="I546" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -25074,7 +25074,7 @@
       </c>
       <c r="I547" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -25119,7 +25119,7 @@
       </c>
       <c r="I548" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -25164,7 +25164,7 @@
       </c>
       <c r="I549" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="I550" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -25254,7 +25254,7 @@
       </c>
       <c r="I551" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -25299,7 +25299,7 @@
       </c>
       <c r="I552" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -25344,7 +25344,7 @@
       </c>
       <c r="I553" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -25389,7 +25389,7 @@
       </c>
       <c r="I554" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -25434,7 +25434,7 @@
       </c>
       <c r="I555" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -25479,7 +25479,7 @@
       </c>
       <c r="I556" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -25524,7 +25524,7 @@
       </c>
       <c r="I557" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -25569,7 +25569,7 @@
       </c>
       <c r="I558" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -25614,7 +25614,7 @@
       </c>
       <c r="I559" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Top-Tether Haken am Autositz klemmt.</t>
         </is>
       </c>
     </row>
@@ -25659,7 +25659,7 @@
       </c>
       <c r="I560" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -25704,7 +25704,7 @@
       </c>
       <c r="I561" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="I562" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="I563" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -25839,7 +25839,7 @@
       </c>
       <c r="I564" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="I565" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -25929,7 +25929,7 @@
       </c>
       <c r="I566" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -25974,7 +25974,7 @@
       </c>
       <c r="I567" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="I568" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -26064,7 +26064,7 @@
       </c>
       <c r="I569" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -26109,7 +26109,7 @@
       </c>
       <c r="I570" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -26154,7 +26154,7 @@
       </c>
       <c r="I571" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -26199,7 +26199,7 @@
       </c>
       <c r="I572" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -26244,7 +26244,7 @@
       </c>
       <c r="I573" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -26289,7 +26289,7 @@
       </c>
       <c r="I574" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -26334,7 +26334,7 @@
       </c>
       <c r="I575" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="I576" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -26424,7 +26424,7 @@
       </c>
       <c r="I577" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -26469,7 +26469,7 @@
       </c>
       <c r="I578" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -26514,7 +26514,7 @@
       </c>
       <c r="I579" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -26559,7 +26559,7 @@
       </c>
       <c r="I580" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="I581" s="2" t="inlineStr">
         <is>
-          <t>Farbe blutet stark aus beim Waschen</t>
+          <t>Nach dem Waschen ist der Strampler eingelaufen und hart.</t>
         </is>
       </c>
     </row>
@@ -26649,7 +26649,7 @@
       </c>
       <c r="I582" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -26694,7 +26694,7 @@
       </c>
       <c r="I583" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="I584" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -26784,7 +26784,7 @@
       </c>
       <c r="I585" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -26829,7 +26829,7 @@
       </c>
       <c r="I586" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Schiebegriff wackelt stark und knackt bei jeder Bordsteinkante.</t>
         </is>
       </c>
     </row>
@@ -26874,7 +26874,7 @@
       </c>
       <c r="I587" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="I588" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Luftreifen hat zum dritten Mal einen Platten.</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="I589" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -27009,7 +27009,7 @@
       </c>
       <c r="I590" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="I591" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
@@ -27099,7 +27099,7 @@
       </c>
       <c r="I592" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -27144,7 +27144,7 @@
       </c>
       <c r="I593" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Auge vom Kuscheltier abgefallen – Verschluckungsgefahr!!!</t>
         </is>
       </c>
     </row>
@@ -27189,7 +27189,7 @@
       </c>
       <c r="I594" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -27234,7 +27234,7 @@
       </c>
       <c r="I595" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="I596" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -27324,7 +27324,7 @@
       </c>
       <c r="I597" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -27369,7 +27369,7 @@
       </c>
       <c r="I598" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Isofix-Fuß rastet nicht ein, Sitz wackelt im Auto.</t>
         </is>
       </c>
     </row>
@@ -27414,7 +27414,7 @@
       </c>
       <c r="I599" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="I600" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Hosenträgergurt lässt sich nicht mehr verkürzen.</t>
         </is>
       </c>
     </row>
@@ -27504,7 +27504,7 @@
       </c>
       <c r="I601" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Reißverschluss am Fußsack klemmt und hat Zähne verloren.</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="I602" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -27594,7 +27594,7 @@
       </c>
       <c r="I603" s="2" t="inlineStr">
         <is>
-          <t>Bezug reißt an der Naht</t>
+          <t>Vorderrad lässt sich nicht mehr schwenken, klemmt ständig.</t>
         </is>
       </c>
     </row>
@@ -27639,7 +27639,7 @@
       </c>
       <c r="I604" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Am Kuscheltier ist die Naht am Ohr aufgetrennt und die Füllung kommt raus.</t>
         </is>
       </c>
     </row>
@@ -27684,7 +27684,7 @@
       </c>
       <c r="I605" s="2" t="inlineStr">
         <is>
-          <t>Druckknöpfe lösen sich</t>
+          <t>Farbe blutet stark aus beim Waschen, alles rosa verfärbt.</t>
         </is>
       </c>
     </row>
@@ -27729,7 +27729,7 @@
       </c>
       <c r="I606" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -27774,7 +27774,7 @@
       </c>
       <c r="I607" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -27819,7 +27819,7 @@
       </c>
       <c r="I608" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Hallo, das Radlager blockiert seit gestern komplett, wir kommen kaum noch vorwärts.</t>
         </is>
       </c>
     </row>
@@ -27864,7 +27864,7 @@
       </c>
       <c r="I609" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -27909,7 +27909,7 @@
       </c>
       <c r="I610" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -27954,7 +27954,7 @@
       </c>
       <c r="I611" s="2" t="inlineStr">
         <is>
-          <t>Auge vom Kuscheltier abgefallen (Verschluckungsgefahr)</t>
+          <t>Kopfstütze am Autositz arretiert nicht in der Höhe.</t>
         </is>
       </c>
     </row>
@@ -27999,7 +27999,7 @@
       </c>
       <c r="I612" s="2" t="inlineStr">
         <is>
-          <t>Stoff am Sitzbezug scheuert durch</t>
+          <t>Plastikteil am Greifling ist angesprungen, scharfe Kante.</t>
         </is>
       </c>
     </row>
@@ -28044,7 +28044,7 @@
       </c>
       <c r="I613" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -28089,7 +28089,7 @@
       </c>
       <c r="I614" s="2" t="inlineStr">
         <is>
-          <t>Gurtschloss lässt sich nicht einrasten</t>
+          <t>Die Druckknöpfe am Body lösen sich nach 2× Waschen.</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="I615" s="2" t="inlineStr">
         <is>
-          <t>Radlager blockiert nach wenigen Wochen</t>
+          <t>Gurtschloss klickt nicht mehr richtig ein, Kind war schon fast raus.</t>
         </is>
       </c>
     </row>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="I616" s="2" t="inlineStr">
         <is>
-          <t>Naht am Ohr aufgetrennt, Füllung kommt raus</t>
+          <t>Bezug am Sitz reißt an der Naht, Stoff ist dünn geworden.</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="I617" s="2" t="inlineStr">
         <is>
-          <t>Isofix-Fuß rastet nicht ein</t>
+          <t>Magnethalter am Verdeck ist abgebrochen.</t>
         </is>
       </c>
     </row>
@@ -28269,7 +28269,7 @@
       </c>
       <c r="I618" s="2" t="inlineStr">
         <is>
-          <t>Schiebegriff wackelt stark</t>
+          <t>Stoff am Sitzbezug scheuert durch, schon ein Loch.</t>
         </is>
       </c>
     </row>
